--- a/lifelib/libraries/annuallife/input.xlsx
+++ b/lifelib/libraries/annuallife/input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fumito\OneDrive\pyproj\lifelib\lifelib\libraries\simplelife\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fumito\OneDrive\pyproj\lifelib\lifelib\libraries\annuallife\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C23FA0F-BAC7-4D0E-88E1-AC2817ADEF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F52927E-A3DC-428A-838A-20023091E751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PolicyData" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Assumption" sheetId="5" r:id="rId5"/>
     <sheet name="AssumptionTables" sheetId="6" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="7" r:id="rId7"/>
+    <sheet name="Risks" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ProductSpec!$B$7:$V$30</definedName>
@@ -27,6 +28,8 @@
     <definedName name="AssumptionTable">Assumption!$B$7:$T$16</definedName>
     <definedName name="ConstParams">OtherParams!$K$7:$L$8</definedName>
     <definedName name="LargePolDiscount">OtherParams!$C$7:$D$9</definedName>
+    <definedName name="LifeCorr">Risks!$D$6:$K$13</definedName>
+    <definedName name="LifeShocks">Risks!$D$20:$H$34</definedName>
     <definedName name="MortalityTables">Mortality!$E$5:$Q$137</definedName>
     <definedName name="PolicyData">PolicyData!$B$7:$O$307</definedName>
     <definedName name="PremiumWaiverCost">OtherParams!$G$7:$H$9</definedName>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="108">
   <si>
     <t>ScenID</t>
   </si>
@@ -288,16 +291,92 @@
   <si>
     <t>Value</t>
   </si>
+  <si>
+    <t>Factor</t>
+  </si>
+  <si>
+    <t>col</t>
+  </si>
+  <si>
+    <t>CorrLife</t>
+  </si>
+  <si>
+    <t>row</t>
+  </si>
+  <si>
+    <t>MORT</t>
+  </si>
+  <si>
+    <t>DISAB</t>
+  </si>
+  <si>
+    <t>LAPSE</t>
+  </si>
+  <si>
+    <t>EXPS</t>
+  </si>
+  <si>
+    <t>REV</t>
+  </si>
+  <si>
+    <t>CAT</t>
+  </si>
+  <si>
+    <t>Shock</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>ExtraKey</t>
+  </si>
+  <si>
+    <t>Risk</t>
+  </si>
+  <si>
+    <t>LONGV</t>
+  </si>
+  <si>
+    <t>FIRST</t>
+  </si>
+  <si>
+    <t>SECOND</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>LIMIT</t>
+  </si>
+  <si>
+    <t>DOWN</t>
+  </si>
+  <si>
+    <t>MASS</t>
+  </si>
+  <si>
+    <t>RETAIL</t>
+  </si>
+  <si>
+    <t>RECOV</t>
+  </si>
+  <si>
+    <t>INFL</t>
+  </si>
+  <si>
+    <t>INST</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.000000_ "/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.0000%"/>
+    <numFmt numFmtId="168" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -451,7 +530,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -550,13 +629,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
@@ -14039,30 +14133,30 @@
       <c r="E5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="34">
-        <v>1</v>
-      </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="34">
+      <c r="F5" s="40">
+        <v>1</v>
+      </c>
+      <c r="G5" s="41"/>
+      <c r="H5" s="40">
         <v>2</v>
       </c>
-      <c r="I5" s="35"/>
-      <c r="J5" s="34">
+      <c r="I5" s="41"/>
+      <c r="J5" s="40">
         <v>3</v>
       </c>
-      <c r="K5" s="35"/>
-      <c r="L5" s="34">
+      <c r="K5" s="41"/>
+      <c r="L5" s="40">
         <v>4</v>
       </c>
-      <c r="M5" s="35"/>
-      <c r="N5" s="34">
+      <c r="M5" s="41"/>
+      <c r="N5" s="40">
         <v>5</v>
       </c>
-      <c r="O5" s="35"/>
-      <c r="P5" s="34">
+      <c r="O5" s="41"/>
+      <c r="P5" s="40">
         <v>6</v>
       </c>
-      <c r="Q5" s="35"/>
+      <c r="Q5" s="41"/>
     </row>
     <row r="6" spans="2:17">
       <c r="B6" s="7" t="s">
@@ -19467,7 +19561,7 @@
       <c r="K7" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="L7" s="36">
+      <c r="L7" s="34">
         <v>0</v>
       </c>
     </row>
@@ -19487,7 +19581,7 @@
       <c r="K8" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="L8" s="36">
+      <c r="L8" s="34">
         <v>0</v>
       </c>
     </row>
@@ -41741,4 +41835,453 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82769BEE-F179-4B57-B794-ECE7AF6CAF28}">
+  <dimension ref="D5:K34"/>
+  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.15"/>
+  <cols>
+    <col min="1" max="3" width="8.69140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.4609375" style="1" customWidth="1"/>
+    <col min="5" max="11" width="11.07421875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.69140625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.69140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="4:11">
+      <c r="D5" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+    </row>
+    <row r="6" spans="4:11">
+      <c r="D6" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="I6" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="J6" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="4:11">
+      <c r="D7" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="38">
+        <v>1</v>
+      </c>
+      <c r="F7" s="38">
+        <v>-0.25</v>
+      </c>
+      <c r="G7" s="38">
+        <v>0.25</v>
+      </c>
+      <c r="H7" s="38">
+        <v>0</v>
+      </c>
+      <c r="I7" s="38">
+        <v>0.25</v>
+      </c>
+      <c r="J7" s="38">
+        <v>0</v>
+      </c>
+      <c r="K7" s="38">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="8" spans="4:11">
+      <c r="D8" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="38">
+        <v>-0.25</v>
+      </c>
+      <c r="F8" s="38">
+        <v>1</v>
+      </c>
+      <c r="G8" s="38">
+        <v>0</v>
+      </c>
+      <c r="H8" s="38">
+        <v>0.25</v>
+      </c>
+      <c r="I8" s="38">
+        <v>0.25</v>
+      </c>
+      <c r="J8" s="38">
+        <v>0.25</v>
+      </c>
+      <c r="K8" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="4:11">
+      <c r="D9" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="38">
+        <v>0.25</v>
+      </c>
+      <c r="F9" s="38">
+        <v>0</v>
+      </c>
+      <c r="G9" s="38">
+        <v>1</v>
+      </c>
+      <c r="H9" s="38">
+        <v>0</v>
+      </c>
+      <c r="I9" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="J9" s="38">
+        <v>0</v>
+      </c>
+      <c r="K9" s="38">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="10" spans="4:11">
+      <c r="D10" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="38">
+        <v>0</v>
+      </c>
+      <c r="F10" s="38">
+        <v>0.25</v>
+      </c>
+      <c r="G10" s="38">
+        <v>0</v>
+      </c>
+      <c r="H10" s="38">
+        <v>1</v>
+      </c>
+      <c r="I10" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="J10" s="38">
+        <v>0</v>
+      </c>
+      <c r="K10" s="38">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="11" spans="4:11">
+      <c r="D11" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="38">
+        <v>0.25</v>
+      </c>
+      <c r="F11" s="38">
+        <v>0.25</v>
+      </c>
+      <c r="G11" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="H11" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="I11" s="38">
+        <v>1</v>
+      </c>
+      <c r="J11" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="K11" s="38">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="12" spans="4:11">
+      <c r="D12" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="38">
+        <v>0</v>
+      </c>
+      <c r="F12" s="38">
+        <v>0.25</v>
+      </c>
+      <c r="G12" s="38">
+        <v>0</v>
+      </c>
+      <c r="H12" s="38">
+        <v>0</v>
+      </c>
+      <c r="I12" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="J12" s="38">
+        <v>1</v>
+      </c>
+      <c r="K12" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="4:11">
+      <c r="D13" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="38">
+        <v>0.25</v>
+      </c>
+      <c r="F13" s="38">
+        <v>0</v>
+      </c>
+      <c r="G13" s="38">
+        <v>0.25</v>
+      </c>
+      <c r="H13" s="38">
+        <v>0.25</v>
+      </c>
+      <c r="I13" s="38">
+        <v>0.25</v>
+      </c>
+      <c r="J13" s="38">
+        <v>0</v>
+      </c>
+      <c r="K13" s="38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="4:8">
+      <c r="D19" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="F19" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="H19" s="36" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="4:8">
+      <c r="D20" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="37">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="21" spans="4:8">
+      <c r="D21" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="37">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22" spans="4:8">
+      <c r="D22" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="H22" s="37">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="23" spans="4:8">
+      <c r="D23" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="H23" s="37">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="24" spans="4:8">
+      <c r="D24" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="H24" s="37">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="25" spans="4:8">
+      <c r="D25" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="37">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="4:8">
+      <c r="D26" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="H26" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="4:8">
+      <c r="D27" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="37">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="4:8">
+      <c r="D28" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" s="37">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="29" spans="4:8">
+      <c r="D29" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="F29" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="G29" s="36"/>
+      <c r="H29" s="37">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="4:8">
+      <c r="D30" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="G30" s="36"/>
+      <c r="H30" s="37">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="31" spans="4:8">
+      <c r="D31" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="37">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="32" spans="4:8">
+      <c r="D32" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="H32" s="37">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="33" spans="4:8">
+      <c r="D33" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="37">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="34" spans="4:8">
+      <c r="D34" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="35">
+        <v>1.5E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>